--- a/SLR/Full-Paper-Read/Paper-Review/PS02.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS02.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
   <si>
     <t>ID</t>
   </si>
@@ -26,8 +26,7 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <t xml:space="preserve">
-The authors of the paper discuss the emergence of new software-intensive system configurations such as cyber-physical, cyber-social, and cloud structures, which offer significant convenience and cost-saving benefits, leading to their rapid and large-scale adoption. However, these new configurations also present unintended problems and vulnerabilities. The authors identify these issues and highlight the need for research and new insights to address them effectively. They emphasize the importance of correcting these vulnerabilities and establishing public trust to prevent potentially counterproductive political intervention. The paper advocates for integrating these concerns into development methodologies and projects, and calls for the creation of necessary theoretical, technological, and educational foundations.</t>
+    <t>The authors discuss the use of Cyber-Physical Systems (CPSs) in large, mobile, and distributed systems like transportation and healthcare, which lead to the development of new cross-CPS applications. These applications enable dynamic, end-to-end scenarios, such as disaster recovery systems. To support this, the authors propose new distributed service composition models that integrate CPS services from different domains to create CPS ecosystems. The paper highlights the advantages of using Cloud-based CPSs, which offer global and rapid access to these services, thereby enhancing the development of CPS ecosystems. However, the dynamic nature of CPS services poses a challenge for service composition. To address this, the authors suggest using models at runtime to create a dynamic middleware framework. This framework facilitates the efficient composition of CPS services by synthesizing software mediators that manage communication between CPS services in the Cloud. The focus of the paper is on supporting the dynamic composition of CPS ecosystems, which can be formed on-demand from existing CPSs, such as spontaneously creating a disaster management system from healthcare and smart transport systems. The authors present basic runtime and mediator models as part of an emergent middleware framework for fast, on-demand service composition in Cloud-based CPSs. Future work will explore the benefits of runtime models in enhancing the safety and reliability of CPS ecosystems.</t>
   </si>
   <si>
     <r>
@@ -37,8 +36,7 @@
         <color theme="1"/>
         <sz val="10.0"/>
       </rPr>
-      <t xml:space="preserve">Software Ecosystems defined:
-(1) </t>
+      <t xml:space="preserve">The authors said: "How to synthesize the composition software? After building the runtime models of two systems, we need synthesis solutions to create a mediator that will implement the composition goals. In particular, it should resolve the differences between the heterogeneous protocol endpoints, and then generate the software that implements this </t>
     </r>
     <r>
       <rPr>
@@ -48,7 +46,7 @@
         <color theme="1"/>
         <sz val="10.0"/>
       </rPr>
-      <t>Cloud:</t>
+      <t xml:space="preserve">mediator </t>
     </r>
     <r>
       <rPr>
@@ -57,311 +55,42 @@
         <color theme="1"/>
         <sz val="10.0"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t>on-the-fly. The generated software will be dynamically deployed between two systems that want to interact. It should be noted that the synthesis process is further supported by ontologies that formalise the domain knowledge."
+2nd reviewer: The authors mention that in their view CPSoS == CPS ecosystems, could be something to keep in mind. Authors also discuss architecture as very central to CPSoS</t>
     </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>a.</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> Frequent difficulty in achieving consistently high average utilization levels; the products appear to hit “turbulence” well below the anticipated levels </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>b.</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> High levels of configuration errors, and difficulty in diagnosing and correcting them. </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>c.</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> Intense confusion and fear among our users and potential users about the privacy and security aspects of co-mingling their data with that of others, and ignorance of what is happening inside of the cloud. </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>SOLUTION</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>a.</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> Fine-grained access control </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>b.</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> High-reliability operations (expressed in terms of availability of service), while never losing or corrupting data </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>c.</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> Key management in configurations with unprecedented numbers of encryption keys. </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>d.</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> Detecting when people have (perhaps inadvertently) created security holes. 
-2) </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>Big Data</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">: we will know less than we have historically known about the range of data to be processed, its formats, and especially its provenance. Testing.  Increasingly-large portions of the data that our systems need to process comes from unvetted sources (e.g., “the net”). How can we provide some sort of “quality / trustworthiness” assessment of the data we are processing, and of the “answers” that we generate?
-3) </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>CPS</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">: Unsolved problems
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">. Authentication
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>b</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">. Built-in protection against unreasonable use.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>c</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">. Social aspects are on a par with the complexity of the technical aspects: • Are ill-defined • Involve many stakeholders with strong and opposing views • Have conditions that change midstream • Are misunderstood until a solution is in hand • After solution, morph into new wicked problems;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>d</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>. key challenges for "wicked problems": • The problem might be too fuzzy or indistinct to permit the definition of complete requirements • The problem might change mid-stream • The stakeholders might not all agree • We might not know all of the stakeholders
-e. RELIABILITY AND SAFETY</t>
-    </r>
   </si>
   <si>
     <t>CPS Case Study / Example availability</t>
   </si>
   <si>
+    <t>Disaster management systems</t>
+  </si>
+  <si>
+    <t>SECO Tools Availability (add repository or website in the comment)</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>&lt;add your comment here if any&gt;</t>
   </si>
   <si>
-    <t>SECO Tools Availability (add repository or website in the comment)</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
   </si>
   <si>
-    <t>Data</t>
-  </si>
-  <si>
     <t>Modeling and Model-Driven Engineering</t>
   </si>
   <si>
+    <t>Continuous software and system engineering</t>
+  </si>
+  <si>
     <t>Requirements engineering</t>
   </si>
   <si>
     <t>n.a.</t>
   </si>
   <si>
-    <t>Reliability, safety, (cyber)security, testing, adaptability, stakeholder engangement</t>
+    <t>Manteinability, Interoperabililty, Scalability</t>
   </si>
   <si>
     <t>Does it contribute to answer RQ1?</t>
@@ -370,18 +99,12 @@
     <t>Y</t>
   </si>
   <si>
-    <t>I like the "wicked problem" discussion in the paper, probably that could be codified as a challenge? Perhaps uncertainty or unknowns in development?</t>
+    <t>Somehow this is also emphasised at runtime, perhaps its own category?</t>
   </si>
   <si>
     <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
   </si>
   <si>
-    <t>Partially</t>
-  </si>
-  <si>
-    <t>No methods and tools, only benefits in therms of sharing of resources (cloud), societal problems solving (e.g., reducing traffic congestion, improving health-care outcomes), convenience and cost-savings</t>
-  </si>
-  <si>
     <t>Does it contribute to answer RQ2?</t>
   </si>
   <si>
@@ -391,10 +114,13 @@
     <t>Application Domain Independent</t>
   </si>
   <si>
+    <t>Emergency Health Care Systems, Emergency Rescue Systems, Emergency Telecommunication Systems, Smart Transportation</t>
+  </si>
+  <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
   </si>
   <si>
-    <t>Since it says (keynote) in the title, I am not sure this exactly qualifies as a study? I liked to read it, but it felt very anecdotal</t>
+    <t>NOTE: more related to Cyber-Physical System of Systems</t>
   </si>
   <si>
     <t>RQ1: In the SECO, what are the main challenges faced during the CPS development?</t>
@@ -506,7 +232,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -532,6 +258,11 @@
       <name val="Arial"/>
     </font>
     <font/>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -870,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -903,7 +634,7 @@
     </xf>
     <xf borderId="16" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="15" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="17" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
@@ -924,8 +655,14 @@
     <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
@@ -933,90 +670,90 @@
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="22" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="22" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="23" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="23" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="24" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="24" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="24" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1314,7 +1051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="137.25" customHeight="1">
+    <row r="3" ht="261.0" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
@@ -1333,7 +1070,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="17">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1360,7 +1097,7 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1368,39 +1105,39 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="16">
         <v>5.0</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="25"/>
@@ -1408,7 +1145,7 @@
       <c r="G7" s="25"/>
       <c r="H7" s="18"/>
       <c r="I7" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -1416,18 +1153,18 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="24" t="s">
         <v>20</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>9</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
       <c r="H8" s="18"/>
-      <c r="I8" s="23" t="s">
-        <v>21</v>
+      <c r="I8" s="28" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1435,10 +1172,10 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>9</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
@@ -1446,71 +1183,75 @@
       <c r="G9" s="25"/>
       <c r="H9" s="18"/>
       <c r="I9" s="21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="16">
         <v>8.0</v>
       </c>
       <c r="B10" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="D10" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="16">
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>Quality!C29</f>
-        <v>5.37037037</v>
+        <v>5.740740741</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
-      <c r="I11" s="32" t="s">
-        <v>26</v>
+      <c r="I11" s="21" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
       <c r="B14" s="33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1"/>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="B16" s="34" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="B15" s="33" t="s">
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="B17" s="34" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1"/>
-    <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
     <row r="20" ht="15.75" customHeight="1"/>
@@ -2565,362 +2306,362 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34"/>
-      <c r="B1" s="35" t="s">
+      <c r="A1" s="35"/>
+      <c r="B1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="41">
+      <c r="C2" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="43"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="44"/>
+      <c r="B3" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="D3" s="37"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="43"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="44"/>
+      <c r="B4" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="42">
+        <v>1.0</v>
+      </c>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="44"/>
+      <c r="B5" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="45">
         <v>0.5</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="42"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="43"/>
-      <c r="B3" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="44">
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="44"/>
+      <c r="B6" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="42">
         <v>1.0</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="42"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="43"/>
-      <c r="B4" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="41">
-        <v>0.0</v>
-      </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="43"/>
-      <c r="B5" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="44">
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="46"/>
+      <c r="B7" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="42">
         <v>1.0</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="43"/>
-      <c r="B6" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="44">
-        <v>1.0</v>
-      </c>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="45"/>
-      <c r="B7" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="44">
-        <v>1.0</v>
-      </c>
-      <c r="D7" s="46">
+      <c r="D7" s="47">
         <f>COUNTIF(B2:B7,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="47">
         <f>(SUM(C2:C7)/D7)*10</f>
-        <v>7.5</v>
+        <v>9.166666667</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="50">
         <v>0.0</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
     </row>
     <row r="9">
-      <c r="A9" s="43"/>
-      <c r="B9" s="48" t="s">
+      <c r="A9" s="44"/>
+      <c r="B9" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="49">
+      <c r="C9" s="50">
         <v>0.0</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
     </row>
     <row r="10">
-      <c r="A10" s="43"/>
-      <c r="B10" s="48" t="s">
+      <c r="A10" s="44"/>
+      <c r="B10" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="49">
+      <c r="C10" s="50">
         <v>0.5</v>
       </c>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
     </row>
     <row r="11">
-      <c r="A11" s="43"/>
-      <c r="B11" s="48" t="s">
+      <c r="A11" s="44"/>
+      <c r="B11" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="49">
+      <c r="C11" s="50">
         <v>0.0</v>
       </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
     </row>
     <row r="12">
-      <c r="A12" s="43"/>
-      <c r="B12" s="48" t="s">
+      <c r="A12" s="44"/>
+      <c r="B12" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="49">
+      <c r="C12" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="44"/>
+      <c r="B13" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="44"/>
+      <c r="B14" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="51">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="44"/>
+      <c r="B15" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="44"/>
+      <c r="B16" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="50">
         <v>0.0</v>
       </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="43"/>
-      <c r="B13" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="49">
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="44"/>
+      <c r="B17" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="50">
         <v>0.5</v>
       </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="43"/>
-      <c r="B14" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="49">
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="44"/>
+      <c r="B18" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="51">
+        <v>1.0</v>
+      </c>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="46"/>
+      <c r="B19" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="50">
         <v>0.0</v>
       </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="43"/>
-      <c r="B15" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="49">
-        <v>0.0</v>
-      </c>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="43"/>
-      <c r="B16" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="43"/>
-      <c r="B17" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="43"/>
-      <c r="B18" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="45"/>
-      <c r="B19" s="48" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="49">
-        <v>0.0</v>
-      </c>
-      <c r="D19" s="46">
+      <c r="D19" s="47">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
         <v>12</v>
       </c>
-      <c r="E19" s="46">
+      <c r="E19" s="47">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="53">
+      <c r="C20" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="44"/>
+      <c r="B21" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="54">
+        <v>0.0</v>
+      </c>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="44"/>
+      <c r="B22" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="55">
         <v>1.0</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="43"/>
-      <c r="B21" s="52" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="54">
-        <v>0.5</v>
-      </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="43"/>
-      <c r="B22" s="52" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="53">
-        <v>1.0</v>
-      </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
     </row>
     <row r="23">
-      <c r="A23" s="43"/>
-      <c r="B23" s="52" t="s">
+      <c r="A23" s="44"/>
+      <c r="B23" s="53" t="s">
         <v>55</v>
       </c>
       <c r="C23" s="54">
         <v>0.5</v>
       </c>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="42"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="43"/>
     </row>
     <row r="24">
-      <c r="A24" s="43"/>
-      <c r="B24" s="52" t="s">
+      <c r="A24" s="44"/>
+      <c r="B24" s="53" t="s">
         <v>56</v>
       </c>
       <c r="C24" s="54">
         <v>0.0</v>
       </c>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="42"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="43"/>
     </row>
     <row r="25">
-      <c r="A25" s="45"/>
-      <c r="B25" s="52" t="s">
+      <c r="A25" s="46"/>
+      <c r="B25" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="53">
+      <c r="C25" s="55">
         <v>1.0</v>
       </c>
-      <c r="D25" s="55">
+      <c r="D25" s="56">
         <f>COUNTIF(B20:B25,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E25" s="55">
+      <c r="E25" s="56">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>6.666666667</v>
-      </c>
-      <c r="F25" s="42"/>
+        <v>5</v>
+      </c>
+      <c r="F25" s="43"/>
     </row>
     <row r="26">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="58">
+      <c r="C26" s="59">
         <v>1.0</v>
       </c>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="42"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="43"/>
     </row>
     <row r="27">
-      <c r="A27" s="43"/>
-      <c r="B27" s="57" t="s">
+      <c r="A27" s="44"/>
+      <c r="B27" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="58">
+      <c r="C27" s="60">
+        <v>0.5</v>
+      </c>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="43"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="46"/>
+      <c r="B28" s="58" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="59">
         <v>1.0</v>
       </c>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="42"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="45"/>
-      <c r="B28" s="57" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="58">
-        <v>1.0</v>
-      </c>
-      <c r="D28" s="55">
+      <c r="D28" s="56">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
         <v>3</v>
       </c>
-      <c r="E28" s="55">
+      <c r="E28" s="56">
         <f>(SUM(C26:C28)/D28)*10</f>
-        <v>10</v>
-      </c>
-      <c r="F28" s="42"/>
+        <v>8.333333333</v>
+      </c>
+      <c r="F28" s="43"/>
     </row>
     <row r="29">
-      <c r="B29" s="59">
+      <c r="B29" s="61">
         <f>COUNTIF(B2:B28,"&lt;&gt;text")</f>
         <v>27</v>
       </c>
-      <c r="C29" s="59">
+      <c r="C29" s="61">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>5.37037037</v>
+        <v>5.740740741</v>
       </c>
     </row>
   </sheetData>
